--- a/diseases/d211/2020-2025.xlsx
+++ b/diseases/d211/2020-2025.xlsx
@@ -1012,7 +1012,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
@@ -1905,7 +1905,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2556,7 +2556,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -4267,7 +4267,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -5569,7 +5569,7 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
@@ -6220,7 +6220,7 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -6871,7 +6871,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7522,7 +7522,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7764,7 +7764,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -8173,7 +8173,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -8415,7 +8415,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8824,7 +8824,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -9066,7 +9066,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -9475,7 +9475,7 @@
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
@@ -9717,7 +9717,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -10368,7 +10368,7 @@
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
@@ -10777,7 +10777,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -11019,7 +11019,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -11428,7 +11428,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11670,7 +11670,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -12079,7 +12079,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -12321,7 +12321,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12730,7 +12730,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12972,7 +12972,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -13381,7 +13381,7 @@
       </c>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -13623,7 +13623,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -14032,7 +14032,7 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -14274,7 +14274,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -14683,7 +14683,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -14925,7 +14925,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -15334,7 +15334,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -15576,7 +15576,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -15985,7 +15985,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -16227,7 +16227,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -16636,7 +16636,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16878,7 +16878,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -17287,7 +17287,7 @@
       </c>
       <c r="AJ78" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK78" t="inlineStr">
@@ -17529,7 +17529,7 @@
       </c>
       <c r="AJ79" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK79" t="inlineStr">
@@ -17938,7 +17938,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -18180,7 +18180,7 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -18589,7 +18589,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -18831,7 +18831,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -19240,7 +19240,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -19482,7 +19482,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -19891,7 +19891,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -20133,7 +20133,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -20542,7 +20542,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -20784,7 +20784,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
@@ -21193,7 +21193,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -21435,7 +21435,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -21844,7 +21844,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -22086,7 +22086,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -22495,7 +22495,7 @@
       </c>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -22737,7 +22737,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -23146,7 +23146,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -23388,7 +23388,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -23797,7 +23797,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -24039,7 +24039,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -24448,7 +24448,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -24690,7 +24690,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -25099,7 +25099,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -25341,7 +25341,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -25750,7 +25750,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -25992,7 +25992,7 @@
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -26401,7 +26401,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -26643,7 +26643,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -27052,7 +27052,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -27294,7 +27294,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -27703,7 +27703,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
@@ -27945,7 +27945,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -28354,7 +28354,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -28596,7 +28596,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -29005,7 +29005,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -29247,7 +29247,7 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -29656,7 +29656,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -29898,7 +29898,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
@@ -30307,7 +30307,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -30549,7 +30549,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
@@ -30958,7 +30958,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -31200,7 +31200,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -31609,7 +31609,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -31851,7 +31851,7 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -32260,7 +32260,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
@@ -32502,7 +32502,7 @@
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
@@ -32911,7 +32911,7 @@
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
@@ -33153,7 +33153,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -33562,7 +33562,7 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
@@ -33804,7 +33804,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -34213,7 +34213,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -34455,7 +34455,7 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
@@ -34864,7 +34864,7 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
@@ -35106,7 +35106,7 @@
       </c>
       <c r="AJ160" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK160" t="inlineStr">
@@ -35515,7 +35515,7 @@
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
@@ -35757,7 +35757,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -36166,7 +36166,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -36408,7 +36408,7 @@
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK166" t="inlineStr">
@@ -36817,7 +36817,7 @@
       </c>
       <c r="AJ168" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK168" t="inlineStr">
@@ -37059,7 +37059,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -37468,7 +37468,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -37710,7 +37710,7 @@
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK172" t="inlineStr">
@@ -38119,7 +38119,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
@@ -38361,7 +38361,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -38770,7 +38770,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -39012,7 +39012,7 @@
       </c>
       <c r="AJ178" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK178" t="inlineStr">
@@ -39421,7 +39421,7 @@
       </c>
       <c r="AJ180" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK180" t="inlineStr">
@@ -39663,7 +39663,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -40072,7 +40072,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -40314,7 +40314,7 @@
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK184" t="inlineStr">
@@ -40723,7 +40723,7 @@
       </c>
       <c r="AJ186" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK186" t="inlineStr">
@@ -40965,7 +40965,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -41374,7 +41374,7 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
@@ -41616,7 +41616,7 @@
       </c>
       <c r="AJ190" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK190" t="inlineStr">
@@ -42025,7 +42025,7 @@
       </c>
       <c r="AJ192" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK192" t="inlineStr">
@@ -42267,7 +42267,7 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
@@ -42676,7 +42676,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -42918,7 +42918,7 @@
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK196" t="inlineStr">
@@ -43327,7 +43327,7 @@
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK198" t="inlineStr">
@@ -43569,7 +43569,7 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
@@ -43978,7 +43978,7 @@
       </c>
       <c r="AJ201" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK201" t="inlineStr">
@@ -44220,7 +44220,7 @@
       </c>
       <c r="AJ202" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK202" t="inlineStr">
@@ -44629,7 +44629,7 @@
       </c>
       <c r="AJ204" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK204" t="inlineStr">
@@ -44871,7 +44871,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -45280,7 +45280,7 @@
       </c>
       <c r="AJ207" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK207" t="inlineStr">
@@ -45522,7 +45522,7 @@
       </c>
       <c r="AJ208" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK208" t="inlineStr">
@@ -45931,7 +45931,7 @@
       </c>
       <c r="AJ210" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK210" t="inlineStr">
@@ -46173,7 +46173,7 @@
       </c>
       <c r="AJ211" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK211" t="inlineStr">
@@ -46582,7 +46582,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -46824,7 +46824,7 @@
       </c>
       <c r="AJ214" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK214" t="inlineStr">
@@ -47233,7 +47233,7 @@
       </c>
       <c r="AJ216" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK216" t="inlineStr">
@@ -47475,7 +47475,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -47884,7 +47884,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -48126,7 +48126,7 @@
       </c>
       <c r="AJ220" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK220" t="inlineStr">
@@ -48535,7 +48535,7 @@
       </c>
       <c r="AJ222" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK222" t="inlineStr">
@@ -48777,7 +48777,7 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
@@ -49186,7 +49186,7 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
@@ -49428,7 +49428,7 @@
       </c>
       <c r="AJ226" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK226" t="inlineStr">
@@ -49837,7 +49837,7 @@
       </c>
       <c r="AJ228" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK228" t="inlineStr">
@@ -50079,7 +50079,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -50488,7 +50488,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -50730,7 +50730,7 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK232" t="inlineStr">
@@ -51139,7 +51139,7 @@
       </c>
       <c r="AJ234" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK234" t="inlineStr">
@@ -51381,7 +51381,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -51790,7 +51790,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -52032,7 +52032,7 @@
       </c>
       <c r="AJ238" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK238" t="inlineStr">
@@ -52441,7 +52441,7 @@
       </c>
       <c r="AJ240" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK240" t="inlineStr">
@@ -52683,7 +52683,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">
@@ -53092,7 +53092,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -53334,7 +53334,7 @@
       </c>
       <c r="AJ244" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK244" t="inlineStr">
@@ -53743,7 +53743,7 @@
       </c>
       <c r="AJ246" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK246" t="inlineStr">
@@ -53985,7 +53985,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -54394,7 +54394,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -54636,7 +54636,7 @@
       </c>
       <c r="AJ250" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK250" t="inlineStr">
@@ -55045,7 +55045,7 @@
       </c>
       <c r="AJ252" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK252" t="inlineStr">
@@ -55287,7 +55287,7 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">
@@ -55696,7 +55696,7 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
@@ -55938,7 +55938,7 @@
       </c>
       <c r="AJ256" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK256" t="inlineStr">
@@ -56347,7 +56347,7 @@
       </c>
       <c r="AJ258" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK258" t="inlineStr">
@@ -56589,7 +56589,7 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
@@ -56998,7 +56998,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -57240,7 +57240,7 @@
       </c>
       <c r="AJ262" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK262" t="inlineStr">
@@ -57649,7 +57649,7 @@
       </c>
       <c r="AJ264" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK264" t="inlineStr">
@@ -57891,7 +57891,7 @@
       </c>
       <c r="AJ265" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK265" t="inlineStr">
@@ -58300,7 +58300,7 @@
       </c>
       <c r="AJ267" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK267" t="inlineStr">
@@ -58542,7 +58542,7 @@
       </c>
       <c r="AJ268" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK268" t="inlineStr">
@@ -58951,7 +58951,7 @@
       </c>
       <c r="AJ270" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK270" t="inlineStr">
@@ -59193,7 +59193,7 @@
       </c>
       <c r="AJ271" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK271" t="inlineStr">
@@ -59602,7 +59602,7 @@
       </c>
       <c r="AJ273" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK273" t="inlineStr">
@@ -59844,7 +59844,7 @@
       </c>
       <c r="AJ274" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK274" t="inlineStr">
@@ -60253,7 +60253,7 @@
       </c>
       <c r="AJ276" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK276" t="inlineStr">
@@ -60495,7 +60495,7 @@
       </c>
       <c r="AJ277" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK277" t="inlineStr">
@@ -60904,7 +60904,7 @@
       </c>
       <c r="AJ279" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK279" t="inlineStr">
@@ -61146,7 +61146,7 @@
       </c>
       <c r="AJ280" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK280" t="inlineStr">
@@ -61555,7 +61555,7 @@
       </c>
       <c r="AJ282" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK282" t="inlineStr">
@@ -61797,7 +61797,7 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
@@ -62206,7 +62206,7 @@
       </c>
       <c r="AJ285" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK285" t="inlineStr">
@@ -62448,7 +62448,7 @@
       </c>
       <c r="AJ286" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK286" t="inlineStr">
@@ -62857,7 +62857,7 @@
       </c>
       <c r="AJ288" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK288" t="inlineStr">
@@ -63099,7 +63099,7 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">
@@ -63508,7 +63508,7 @@
       </c>
       <c r="AJ291" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK291" t="inlineStr">
@@ -63750,7 +63750,7 @@
       </c>
       <c r="AJ292" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK292" t="inlineStr">
@@ -64159,7 +64159,7 @@
       </c>
       <c r="AJ294" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK294" t="inlineStr">
@@ -64401,7 +64401,7 @@
       </c>
       <c r="AJ295" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK295" t="inlineStr">
@@ -64810,7 +64810,7 @@
       </c>
       <c r="AJ297" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK297" t="inlineStr">
@@ -65052,7 +65052,7 @@
       </c>
       <c r="AJ298" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK298" t="inlineStr">
@@ -65461,7 +65461,7 @@
       </c>
       <c r="AJ300" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK300" t="inlineStr">
@@ -65703,7 +65703,7 @@
       </c>
       <c r="AJ301" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK301" t="inlineStr">
@@ -66112,7 +66112,7 @@
       </c>
       <c r="AJ303" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK303" t="inlineStr">
@@ -66354,7 +66354,7 @@
       </c>
       <c r="AJ304" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK304" t="inlineStr">
@@ -66763,7 +66763,7 @@
       </c>
       <c r="AJ306" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK306" t="inlineStr">
@@ -67005,7 +67005,7 @@
       </c>
       <c r="AJ307" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK307" t="inlineStr">
@@ -67414,7 +67414,7 @@
       </c>
       <c r="AJ309" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK309" t="inlineStr">
@@ -67656,7 +67656,7 @@
       </c>
       <c r="AJ310" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK310" t="inlineStr">
@@ -68065,7 +68065,7 @@
       </c>
       <c r="AJ312" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK312" t="inlineStr">
@@ -68307,7 +68307,7 @@
       </c>
       <c r="AJ313" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK313" t="inlineStr">

--- a/diseases/d211/2020-2025.xlsx
+++ b/diseases/d211/2020-2025.xlsx
@@ -765,14 +765,12 @@
       <c r="O2" t="n">
         <v>575</v>
       </c>
+      <c r="P2" t="n">
+        <v>575</v>
+      </c>
       <c r="R2" t="n">
         <v>0.1664608482015126</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -785,23 +783,13 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
       </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV2" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -915,14 +903,12 @@
       <c r="O3" t="n">
         <v>509</v>
       </c>
+      <c r="P3" t="n">
+        <v>509</v>
+      </c>
       <c r="R3" t="n">
         <v>0.147354037799252</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -935,23 +921,13 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
       </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV3" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -1065,14 +1041,12 @@
       <c r="O4" t="n">
         <v>587</v>
       </c>
+      <c r="P4" t="n">
+        <v>587</v>
+      </c>
       <c r="R4" t="n">
         <v>0.1699348137291963</v>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1085,23 +1059,13 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
       </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV4" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -1215,14 +1179,12 @@
       <c r="O5" t="n">
         <v>798</v>
       </c>
+      <c r="P5" t="n">
+        <v>798</v>
+      </c>
       <c r="R5" t="n">
         <v>0.2310187075909687</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1235,23 +1197,13 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
       </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV5" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -1365,14 +1317,12 @@
       <c r="O6" t="n">
         <v>712</v>
       </c>
+      <c r="P6" t="n">
+        <v>712</v>
+      </c>
       <c r="R6" t="n">
         <v>0.2061219546425686</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1385,23 +1335,13 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
       </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV6" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -1515,14 +1455,12 @@
       <c r="O7" t="n">
         <v>872</v>
       </c>
+      <c r="P7" t="n">
+        <v>872</v>
+      </c>
       <c r="R7" t="n">
         <v>0.2524414950116851</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1535,23 +1473,13 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
       </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV7" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -1665,14 +1593,12 @@
       <c r="O8" t="n">
         <v>967</v>
       </c>
+      <c r="P8" t="n">
+        <v>967</v>
+      </c>
       <c r="R8" t="n">
         <v>0.2799437221058481</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1685,23 +1611,13 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
       </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV8" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -1815,14 +1731,12 @@
       <c r="O9" t="n">
         <v>964</v>
       </c>
+      <c r="P9" t="n">
+        <v>964</v>
+      </c>
       <c r="R9" t="n">
         <v>0.2790752307239271</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1835,23 +1749,13 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
       </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV9" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -1965,14 +1869,12 @@
       <c r="O10" t="n">
         <v>897</v>
       </c>
+      <c r="P10" t="n">
+        <v>897</v>
+      </c>
       <c r="R10" t="n">
         <v>0.2596789231943596</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1985,23 +1887,13 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
       </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV10" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -2115,14 +2007,12 @@
       <c r="O11" t="n">
         <v>871</v>
       </c>
+      <c r="P11" t="n">
+        <v>871</v>
+      </c>
       <c r="R11" t="n">
         <v>0.2521519978843781</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2135,23 +2025,13 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
       </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV11" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -2265,14 +2145,12 @@
       <c r="O12" t="n">
         <v>868</v>
       </c>
+      <c r="P12" t="n">
+        <v>868</v>
+      </c>
       <c r="R12" t="n">
         <v>0.2512835065024572</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2285,23 +2163,13 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
       </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV12" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -2415,14 +2283,12 @@
       <c r="O13" t="n">
         <v>966</v>
       </c>
+      <c r="P13" t="n">
+        <v>966</v>
+      </c>
       <c r="R13" t="n">
         <v>0.2796542249785411</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2435,23 +2301,13 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
       </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV13" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -2565,14 +2421,12 @@
       <c r="O14" t="n">
         <v>781</v>
       </c>
+      <c r="P14" t="n">
+        <v>781</v>
+      </c>
       <c r="R14" t="n">
         <v>0.2260972564267501</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2585,23 +2439,13 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
       </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV14" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -2715,14 +2559,12 @@
       <c r="O15" t="n">
         <v>770</v>
       </c>
+      <c r="P15" t="n">
+        <v>770</v>
+      </c>
       <c r="R15" t="n">
         <v>0.2229127880263733</v>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2735,23 +2577,13 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
       </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV15" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -2865,14 +2697,12 @@
       <c r="O16" t="n">
         <v>805</v>
       </c>
+      <c r="P16" t="n">
+        <v>805</v>
+      </c>
       <c r="R16" t="n">
         <v>0.2330451874821176</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2885,23 +2715,13 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
       </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV16" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -3015,14 +2835,12 @@
       <c r="O17" t="n">
         <v>854</v>
       </c>
+      <c r="P17" t="n">
+        <v>854</v>
+      </c>
       <c r="R17" t="n">
         <v>0.2472305467201595</v>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3035,23 +2853,13 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
       </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV17" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -3165,14 +2973,12 @@
       <c r="O18" t="n">
         <v>657</v>
       </c>
+      <c r="P18" t="n">
+        <v>657</v>
+      </c>
       <c r="R18" t="n">
         <v>0.1901996126406848</v>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3185,23 +2991,13 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
       </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV18" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -3315,14 +3111,12 @@
       <c r="O19" t="n">
         <v>974</v>
       </c>
+      <c r="P19" t="n">
+        <v>974</v>
+      </c>
       <c r="R19" t="n">
         <v>0.2819702019969969</v>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3335,23 +3129,13 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
       </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV19" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -3465,14 +3249,12 @@
       <c r="O20" t="n">
         <v>804</v>
       </c>
+      <c r="P20" t="n">
+        <v>804</v>
+      </c>
       <c r="R20" t="n">
         <v>0.2327556903548106</v>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3485,23 +3267,13 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
       </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV20" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -3615,14 +3387,12 @@
       <c r="O21" t="n">
         <v>794</v>
       </c>
+      <c r="P21" t="n">
+        <v>794</v>
+      </c>
       <c r="R21" t="n">
         <v>0.2298607190817408</v>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3635,23 +3405,13 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
       </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV21" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -3765,14 +3525,12 @@
       <c r="O22" t="n">
         <v>652</v>
       </c>
+      <c r="P22" t="n">
+        <v>652</v>
+      </c>
       <c r="R22" t="n">
         <v>0.1887521270041499</v>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3785,23 +3543,13 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
       </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV22" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -3915,14 +3663,12 @@
       <c r="O23" t="n">
         <v>567</v>
       </c>
+      <c r="P23" t="n">
+        <v>567</v>
+      </c>
       <c r="R23" t="n">
         <v>0.1641448711830567</v>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3935,23 +3681,13 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
       </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV23" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -4065,14 +3801,12 @@
       <c r="O24" t="n">
         <v>662</v>
       </c>
+      <c r="P24" t="n">
+        <v>662</v>
+      </c>
       <c r="R24" t="n">
         <v>0.1916470982772197</v>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4085,23 +3819,13 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
       </c>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV24" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -4215,14 +3939,12 @@
       <c r="O25" t="n">
         <v>752</v>
       </c>
+      <c r="P25" t="n">
+        <v>752</v>
+      </c>
       <c r="R25" t="n">
         <v>0.2177018397348477</v>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4235,23 +3957,13 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
       </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV25" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -4365,14 +4077,12 @@
       <c r="O26" t="n">
         <v>754</v>
       </c>
+      <c r="P26" t="n">
+        <v>754</v>
+      </c>
       <c r="R26" t="n">
         <v>0.2182808339894617</v>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4385,23 +4095,13 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR26" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
       </c>
-      <c r="AU26" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV26" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -4515,14 +4215,12 @@
       <c r="O27" t="n">
         <v>812</v>
       </c>
+      <c r="P27" t="n">
+        <v>812</v>
+      </c>
       <c r="R27" t="n">
         <v>0.2350716673732665</v>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4535,23 +4233,13 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
       </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV27" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -4665,14 +4353,12 @@
       <c r="O28" t="n">
         <v>860</v>
       </c>
+      <c r="P28" t="n">
+        <v>860</v>
+      </c>
       <c r="R28" t="n">
         <v>0.2489675294840014</v>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4685,23 +4371,13 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR28" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
       </c>
-      <c r="AU28" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV28" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -4815,14 +4491,12 @@
       <c r="O29" t="n">
         <v>795</v>
       </c>
+      <c r="P29" t="n">
+        <v>795</v>
+      </c>
       <c r="R29" t="n">
         <v>0.2301502162090478</v>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4835,23 +4509,13 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
       </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV29" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -4965,14 +4629,12 @@
       <c r="O30" t="n">
         <v>599</v>
       </c>
+      <c r="P30" t="n">
+        <v>599</v>
+      </c>
       <c r="R30" t="n">
         <v>0.17340877925688</v>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4985,23 +4647,13 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
       </c>
-      <c r="AU30" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV30" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -5115,14 +4767,12 @@
       <c r="O31" t="n">
         <v>739</v>
       </c>
+      <c r="P31" t="n">
+        <v>739</v>
+      </c>
       <c r="R31" t="n">
         <v>0.213938377079857</v>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5135,23 +4785,13 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR31" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
       </c>
-      <c r="AU31" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV31" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -5265,14 +4905,12 @@
       <c r="O32" t="n">
         <v>758</v>
       </c>
+      <c r="P32" t="n">
+        <v>758</v>
+      </c>
       <c r="R32" t="n">
         <v>0.2194388224986896</v>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5285,23 +4923,13 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
       </c>
-      <c r="AU32" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV32" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -5415,14 +5043,12 @@
       <c r="O33" t="n">
         <v>700</v>
       </c>
+      <c r="P33" t="n">
+        <v>700</v>
+      </c>
       <c r="R33" t="n">
         <v>0.2026479891148849</v>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5435,23 +5061,13 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR33" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
       </c>
-      <c r="AU33" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV33" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -5565,14 +5181,12 @@
       <c r="O34" t="n">
         <v>700</v>
       </c>
+      <c r="P34" t="n">
+        <v>700</v>
+      </c>
       <c r="R34" t="n">
         <v>0.2026479891148849</v>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5585,23 +5199,13 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
       </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV34" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -5715,14 +5319,12 @@
       <c r="O35" t="n">
         <v>872</v>
       </c>
+      <c r="P35" t="n">
+        <v>872</v>
+      </c>
       <c r="R35" t="n">
         <v>0.2524414950116851</v>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5735,23 +5337,13 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR35" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
       </c>
-      <c r="AU35" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV35" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -5865,14 +5457,12 @@
       <c r="O36" t="n">
         <v>992</v>
       </c>
+      <c r="P36" t="n">
+        <v>992</v>
+      </c>
       <c r="R36" t="n">
         <v>0.2871811502885225</v>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5885,23 +5475,13 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR36" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
       </c>
-      <c r="AU36" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV36" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -6015,14 +5595,12 @@
       <c r="O37" t="n">
         <v>618</v>
       </c>
+      <c r="P37" t="n">
+        <v>618</v>
+      </c>
       <c r="R37" t="n">
         <v>0.1789092246757126</v>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6035,23 +5613,13 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR37" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
       </c>
-      <c r="AU37" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV37" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -6165,14 +5733,12 @@
       <c r="O38" t="n">
         <v>753</v>
       </c>
+      <c r="P38" t="n">
+        <v>753</v>
+      </c>
       <c r="R38" t="n">
         <v>0.2179913368621547</v>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6185,23 +5751,13 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR38" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
       </c>
-      <c r="AU38" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV38" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -6315,14 +5871,12 @@
       <c r="O39" t="n">
         <v>746</v>
       </c>
+      <c r="P39" t="n">
+        <v>746</v>
+      </c>
       <c r="R39" t="n">
         <v>0.2159648569710059</v>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6335,23 +5889,13 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR39" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="n">
         <v>0</v>
       </c>
-      <c r="AU39" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV39" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -6465,14 +6009,12 @@
       <c r="O40" t="n">
         <v>790</v>
       </c>
+      <c r="P40" t="n">
+        <v>790</v>
+      </c>
       <c r="R40" t="n">
         <v>0.2287027305725129</v>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6485,23 +6027,13 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR40" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
         <v>0</v>
       </c>
-      <c r="AU40" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV40" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -6615,14 +6147,12 @@
       <c r="O41" t="n">
         <v>736</v>
       </c>
+      <c r="P41" t="n">
+        <v>736</v>
+      </c>
       <c r="R41" t="n">
         <v>0.2130698856979361</v>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6635,23 +6165,13 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR41" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
         <v>0</v>
       </c>
-      <c r="AU41" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV41" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -6765,14 +6285,12 @@
       <c r="O42" t="n">
         <v>758</v>
       </c>
+      <c r="P42" t="n">
+        <v>758</v>
+      </c>
       <c r="R42" t="n">
         <v>0.2194388224986896</v>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6785,23 +6303,13 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR42" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
       </c>
-      <c r="AU42" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV42" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -6915,14 +6423,12 @@
       <c r="O43" t="n">
         <v>768</v>
       </c>
+      <c r="P43" t="n">
+        <v>768</v>
+      </c>
       <c r="R43" t="n">
         <v>0.2223337937717594</v>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6935,23 +6441,13 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR43" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
       </c>
-      <c r="AU43" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV43" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -7065,14 +6561,12 @@
       <c r="O44" t="n">
         <v>811</v>
       </c>
+      <c r="P44" t="n">
+        <v>811</v>
+      </c>
       <c r="R44" t="n">
         <v>0.2347821702459595</v>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -7085,23 +6579,13 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR44" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
         <v>0</v>
       </c>
-      <c r="AU44" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV44" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -7215,14 +6699,12 @@
       <c r="O45" t="n">
         <v>639</v>
       </c>
+      <c r="P45" t="n">
+        <v>639</v>
+      </c>
       <c r="R45" t="n">
         <v>0.1849886643491592</v>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -7235,23 +6717,13 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR45" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
         <v>0</v>
       </c>
-      <c r="AU45" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV45" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -7365,14 +6837,12 @@
       <c r="O46" t="n">
         <v>497</v>
       </c>
+      <c r="P46" t="n">
+        <v>497</v>
+      </c>
       <c r="R46" t="n">
         <v>0.1438800722715682</v>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -7385,23 +6855,13 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR46" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="n">
         <v>0</v>
       </c>
-      <c r="AU46" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV46" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -7515,14 +6975,12 @@
       <c r="O47" t="n">
         <v>722</v>
       </c>
+      <c r="P47" t="n">
+        <v>722</v>
+      </c>
       <c r="R47" t="n">
         <v>0.2090169259156384</v>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -7535,23 +6993,13 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR47" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="n">
         <v>0</v>
       </c>
-      <c r="AU47" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV47" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -7665,14 +7113,12 @@
       <c r="O48" t="n">
         <v>709</v>
       </c>
+      <c r="P48" t="n">
+        <v>709</v>
+      </c>
       <c r="R48" t="n">
         <v>0.2052534632606477</v>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -7685,23 +7131,13 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR48" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
         <v>0</v>
       </c>
-      <c r="AU48" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV48" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -7815,14 +7251,12 @@
       <c r="O49" t="n">
         <v>477</v>
       </c>
+      <c r="P49" t="n">
+        <v>477</v>
+      </c>
       <c r="R49" t="n">
         <v>0.1380901297254287</v>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -7835,23 +7269,13 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR49" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
         <v>0</v>
       </c>
-      <c r="AU49" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV49" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -7965,14 +7389,12 @@
       <c r="O50" t="n">
         <v>721</v>
       </c>
+      <c r="P50" t="n">
+        <v>721</v>
+      </c>
       <c r="R50" t="n">
         <v>0.2087274287883314</v>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -7985,23 +7407,13 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR50" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="n">
         <v>0</v>
       </c>
-      <c r="AU50" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV50" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -8115,14 +7527,12 @@
       <c r="O51" t="n">
         <v>699</v>
       </c>
+      <c r="P51" t="n">
+        <v>699</v>
+      </c>
       <c r="R51" t="n">
         <v>0.2023584919875779</v>
       </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -8135,23 +7545,13 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR51" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="n">
         <v>0</v>
       </c>
-      <c r="AU51" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV51" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -8265,14 +7665,12 @@
       <c r="O52" t="n">
         <v>736</v>
       </c>
+      <c r="P52" t="n">
+        <v>736</v>
+      </c>
       <c r="R52" t="n">
         <v>0.2130698856979361</v>
       </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -8285,23 +7683,13 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR52" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="n">
         <v>0</v>
       </c>
-      <c r="AU52" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV52" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -8415,14 +7803,12 @@
       <c r="O53" t="n">
         <v>300</v>
       </c>
+      <c r="P53" t="n">
+        <v>300</v>
+      </c>
       <c r="R53" t="n">
         <v>0.08684913819209351</v>
       </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -8435,23 +7821,13 @@
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR53" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="n">
         <v>0</v>
       </c>
-      <c r="AU53" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV53" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -8565,14 +7941,12 @@
       <c r="O54" t="n">
         <v>446</v>
       </c>
+      <c r="P54" t="n">
+        <v>446</v>
+      </c>
       <c r="R54" t="n">
         <v>0.1284281802440269</v>
       </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -8585,23 +7959,13 @@
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR54" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="n">
         <v>0</v>
       </c>
-      <c r="AU54" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV54" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -8715,14 +8079,12 @@
       <c r="O55" t="n">
         <v>530</v>
       </c>
+      <c r="P55" t="n">
+        <v>530</v>
+      </c>
       <c r="R55" t="n">
         <v>0.152616447375189</v>
       </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -8735,23 +8097,13 @@
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR55" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="n">
         <v>0</v>
       </c>
-      <c r="AU55" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV55" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -8865,14 +8217,12 @@
       <c r="O56" t="n">
         <v>602</v>
       </c>
+      <c r="P56" t="n">
+        <v>602</v>
+      </c>
       <c r="R56" t="n">
         <v>0.1733492477733278</v>
       </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -8885,23 +8235,13 @@
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR56" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr"/>
       <c r="AT56" t="n">
         <v>0</v>
       </c>
-      <c r="AU56" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV56" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -9015,14 +8355,12 @@
       <c r="O57" t="n">
         <v>660</v>
       </c>
+      <c r="P57" t="n">
+        <v>660</v>
+      </c>
       <c r="R57" t="n">
         <v>0.190050670316273</v>
       </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -9035,23 +8373,13 @@
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR57" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="n">
         <v>0</v>
       </c>
-      <c r="AU57" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV57" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -9165,14 +8493,12 @@
       <c r="O58" t="n">
         <v>621</v>
       </c>
+      <c r="P58" t="n">
+        <v>621</v>
+      </c>
       <c r="R58" t="n">
         <v>0.1788204034339478</v>
       </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -9185,23 +8511,13 @@
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR58" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="n">
         <v>0</v>
       </c>
-      <c r="AU58" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV58" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -9315,14 +8631,12 @@
       <c r="O59" t="n">
         <v>813</v>
       </c>
+      <c r="P59" t="n">
+        <v>813</v>
+      </c>
       <c r="R59" t="n">
         <v>0.2341078711623182</v>
       </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -9335,23 +8649,13 @@
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR59" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="n">
         <v>0</v>
       </c>
-      <c r="AU59" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV59" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -9465,14 +8769,12 @@
       <c r="O60" t="n">
         <v>656</v>
       </c>
+      <c r="P60" t="n">
+        <v>656</v>
+      </c>
       <c r="R60" t="n">
         <v>0.188898848071932</v>
       </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -9485,23 +8787,13 @@
       </c>
       <c r="AP60" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR60" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="n">
         <v>0</v>
       </c>
-      <c r="AU60" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV60" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -9615,14 +8907,12 @@
       <c r="O61" t="n">
         <v>709</v>
       </c>
+      <c r="P61" t="n">
+        <v>709</v>
+      </c>
       <c r="R61" t="n">
         <v>0.2041604928094509</v>
       </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -9635,23 +8925,13 @@
       </c>
       <c r="AP61" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR61" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="n">
         <v>0</v>
       </c>
-      <c r="AU61" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV61" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -9765,14 +9045,12 @@
       <c r="O62" t="n">
         <v>804</v>
       </c>
+      <c r="P62" t="n">
+        <v>804</v>
+      </c>
       <c r="R62" t="n">
         <v>0.2315162711125508</v>
       </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -9785,23 +9063,13 @@
       </c>
       <c r="AP62" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR62" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="n">
         <v>0</v>
       </c>
-      <c r="AU62" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV62" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -9915,14 +9183,12 @@
       <c r="O63" t="n">
         <v>669</v>
       </c>
+      <c r="P63" t="n">
+        <v>669</v>
+      </c>
       <c r="R63" t="n">
         <v>0.1926422703660404</v>
       </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -9935,23 +9201,13 @@
       </c>
       <c r="AP63" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR63" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="n">
         <v>0</v>
       </c>
-      <c r="AU63" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV63" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -10065,14 +9321,12 @@
       <c r="O64" t="n">
         <v>635</v>
       </c>
+      <c r="P64" t="n">
+        <v>635</v>
+      </c>
       <c r="R64" t="n">
         <v>0.1828517812891415</v>
       </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -10085,23 +9339,13 @@
       </c>
       <c r="AP64" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR64" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="n">
         <v>0</v>
       </c>
-      <c r="AU64" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV64" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -10215,14 +9459,12 @@
       <c r="O65" t="n">
         <v>683</v>
       </c>
+      <c r="P65" t="n">
+        <v>683</v>
+      </c>
       <c r="R65" t="n">
         <v>0.1966736482212341</v>
       </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -10235,23 +9477,13 @@
       </c>
       <c r="AP65" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR65" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="n">
         <v>0</v>
       </c>
-      <c r="AU65" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV65" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -10365,14 +9597,12 @@
       <c r="O66" t="n">
         <v>641</v>
       </c>
+      <c r="P66" t="n">
+        <v>641</v>
+      </c>
       <c r="R66" t="n">
         <v>0.1845795146556531</v>
       </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -10385,23 +9615,13 @@
       </c>
       <c r="AP66" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR66" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="n">
         <v>0</v>
       </c>
-      <c r="AU66" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV66" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -10515,14 +9735,12 @@
       <c r="O67" t="n">
         <v>604</v>
       </c>
+      <c r="P67" t="n">
+        <v>604</v>
+      </c>
       <c r="R67" t="n">
         <v>0.1739251588954984</v>
       </c>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -10535,23 +9753,13 @@
       </c>
       <c r="AP67" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR67" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="n">
         <v>0</v>
       </c>
-      <c r="AU67" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV67" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -10665,14 +9873,12 @@
       <c r="O68" t="n">
         <v>689</v>
       </c>
+      <c r="P68" t="n">
+        <v>689</v>
+      </c>
       <c r="R68" t="n">
         <v>0.1984013815877456</v>
       </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -10685,23 +9891,13 @@
       </c>
       <c r="AP68" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR68" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="n">
         <v>0</v>
       </c>
-      <c r="AU68" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV68" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -10815,14 +10011,12 @@
       <c r="O69" t="n">
         <v>753</v>
       </c>
+      <c r="P69" t="n">
+        <v>753</v>
+      </c>
       <c r="R69" t="n">
         <v>0.2168305374972024</v>
       </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -10835,23 +10029,13 @@
       </c>
       <c r="AP69" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR69" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="n">
         <v>0</v>
       </c>
-      <c r="AU69" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV69" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -10965,14 +10149,12 @@
       <c r="O70" t="n">
         <v>666</v>
       </c>
+      <c r="P70" t="n">
+        <v>666</v>
+      </c>
       <c r="R70" t="n">
         <v>0.1917784036827846</v>
       </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -10985,23 +10167,13 @@
       </c>
       <c r="AP70" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR70" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="n">
         <v>0</v>
       </c>
-      <c r="AU70" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV70" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -11115,14 +10287,12 @@
       <c r="O71" t="n">
         <v>842</v>
       </c>
+      <c r="P71" t="n">
+        <v>842</v>
+      </c>
       <c r="R71" t="n">
         <v>0.2424585824337908</v>
       </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -11135,23 +10305,13 @@
       </c>
       <c r="AP71" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR71" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="n">
         <v>0</v>
       </c>
-      <c r="AU71" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV71" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -11265,14 +10425,12 @@
       <c r="O72" t="n">
         <v>776</v>
       </c>
+      <c r="P72" t="n">
+        <v>776</v>
+      </c>
       <c r="R72" t="n">
         <v>0.2234535154021635</v>
       </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -11285,23 +10443,13 @@
       </c>
       <c r="AP72" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR72" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="n">
         <v>0</v>
       </c>
-      <c r="AU72" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV72" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -11415,14 +10563,12 @@
       <c r="O73" t="n">
         <v>862</v>
       </c>
+      <c r="P73" t="n">
+        <v>862</v>
+      </c>
       <c r="R73" t="n">
         <v>0.248217693655496</v>
       </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -11435,23 +10581,13 @@
       </c>
       <c r="AP73" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR73" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="n">
         <v>0</v>
       </c>
-      <c r="AU73" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV73" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -11565,14 +10701,12 @@
       <c r="O74" t="n">
         <v>659</v>
       </c>
+      <c r="P74" t="n">
+        <v>659</v>
+      </c>
       <c r="R74" t="n">
         <v>0.1897627147551878</v>
       </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -11585,23 +10719,13 @@
       </c>
       <c r="AP74" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR74" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="n">
         <v>0</v>
       </c>
-      <c r="AU74" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV74" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -11715,14 +10839,12 @@
       <c r="O75" t="n">
         <v>538</v>
       </c>
+      <c r="P75" t="n">
+        <v>538</v>
+      </c>
       <c r="R75" t="n">
         <v>0.1549200918638711</v>
       </c>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -11735,23 +10857,13 @@
       </c>
       <c r="AP75" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR75" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="n">
         <v>0</v>
       </c>
-      <c r="AU75" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV75" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -11865,14 +10977,12 @@
       <c r="O76" t="n">
         <v>652</v>
       </c>
+      <c r="P76" t="n">
+        <v>652</v>
+      </c>
       <c r="R76" t="n">
         <v>0.187747025827591</v>
       </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -11885,23 +10995,13 @@
       </c>
       <c r="AP76" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR76" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="n">
         <v>0</v>
       </c>
-      <c r="AU76" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV76" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -12015,14 +11115,12 @@
       <c r="O77" t="n">
         <v>630</v>
       </c>
+      <c r="P77" t="n">
+        <v>630</v>
+      </c>
       <c r="R77" t="n">
         <v>0.1814120034837152</v>
       </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -12035,23 +11133,13 @@
       </c>
       <c r="AP77" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR77" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="n">
         <v>0</v>
       </c>
-      <c r="AU77" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV77" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -12165,14 +11253,12 @@
       <c r="O78" t="n">
         <v>742</v>
       </c>
+      <c r="P78" t="n">
+        <v>742</v>
+      </c>
       <c r="R78" t="n">
         <v>0.2136630263252645</v>
       </c>
-      <c r="S78" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -12185,23 +11271,13 @@
       </c>
       <c r="AP78" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR78" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="n">
         <v>0</v>
       </c>
-      <c r="AU78" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV78" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -12315,14 +11391,12 @@
       <c r="O79" t="n">
         <v>569</v>
       </c>
+      <c r="P79" t="n">
+        <v>569</v>
+      </c>
       <c r="R79" t="n">
         <v>0.1638467142575142</v>
       </c>
-      <c r="S79" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -12335,23 +11409,13 @@
       </c>
       <c r="AP79" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR79" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="n">
         <v>0</v>
       </c>
-      <c r="AU79" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV79" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -12465,14 +11529,12 @@
       <c r="O80" t="n">
         <v>475</v>
       </c>
+      <c r="P80" t="n">
+        <v>475</v>
+      </c>
       <c r="R80" t="n">
         <v>0.1367788915154995</v>
       </c>
-      <c r="S80" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -12485,23 +11547,13 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR80" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="n">
         <v>0</v>
       </c>
-      <c r="AU80" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV80" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -12615,14 +11667,12 @@
       <c r="O81" t="n">
         <v>623</v>
       </c>
+      <c r="P81" t="n">
+        <v>623</v>
+      </c>
       <c r="R81" t="n">
         <v>0.1793963145561183</v>
       </c>
-      <c r="S81" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -12635,23 +11685,13 @@
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR81" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="n">
         <v>0</v>
       </c>
-      <c r="AU81" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV81" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -12765,14 +11805,12 @@
       <c r="O82" t="n">
         <v>670</v>
       </c>
+      <c r="P82" t="n">
+        <v>670</v>
+      </c>
       <c r="R82" t="n">
         <v>0.1929302259271257</v>
       </c>
-      <c r="S82" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -12785,23 +11823,13 @@
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR82" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="n">
         <v>0</v>
       </c>
-      <c r="AU82" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV82" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -12915,14 +11943,12 @@
       <c r="O83" t="n">
         <v>584</v>
       </c>
+      <c r="P83" t="n">
+        <v>584</v>
+      </c>
       <c r="R83" t="n">
         <v>0.1681660476737931</v>
       </c>
-      <c r="S83" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -12935,23 +11961,13 @@
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR83" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="n">
         <v>0</v>
       </c>
-      <c r="AU83" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV83" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -13065,14 +12081,12 @@
       <c r="O84" t="n">
         <v>711</v>
       </c>
+      <c r="P84" t="n">
+        <v>711</v>
+      </c>
       <c r="R84" t="n">
         <v>0.2047364039316214</v>
       </c>
-      <c r="S84" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -13085,23 +12099,13 @@
       </c>
       <c r="AP84" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR84" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS84" t="inlineStr"/>
       <c r="AT84" t="n">
         <v>0</v>
       </c>
-      <c r="AU84" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV84" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -13215,14 +12219,12 @@
       <c r="O85" t="n">
         <v>574</v>
       </c>
+      <c r="P85" t="n">
+        <v>574</v>
+      </c>
       <c r="R85" t="n">
         <v>0.1652864920629405</v>
       </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -13235,23 +12237,13 @@
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR85" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="n">
         <v>0</v>
       </c>
-      <c r="AU85" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV85" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -13365,14 +12357,12 @@
       <c r="O86" t="n">
         <v>757</v>
       </c>
+      <c r="P86" t="n">
+        <v>757</v>
+      </c>
       <c r="R86" t="n">
         <v>0.2179823597415435</v>
       </c>
-      <c r="S86" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -13385,23 +12375,13 @@
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR86" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="n">
         <v>0</v>
       </c>
-      <c r="AU86" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV86" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -13515,14 +12495,12 @@
       <c r="O87" t="n">
         <v>691</v>
       </c>
+      <c r="P87" t="n">
+        <v>691</v>
+      </c>
       <c r="R87" t="n">
         <v>0.1989772927099162</v>
       </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -13535,23 +12513,13 @@
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR87" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="n">
         <v>0</v>
       </c>
-      <c r="AU87" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV87" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -13665,14 +12633,12 @@
       <c r="O88" t="n">
         <v>632</v>
       </c>
+      <c r="P88" t="n">
+        <v>632</v>
+      </c>
       <c r="R88" t="n">
         <v>0.1819879146058857</v>
       </c>
-      <c r="S88" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -13685,23 +12651,13 @@
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR88" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="n">
         <v>0</v>
       </c>
-      <c r="AU88" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV88" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -13815,14 +12771,12 @@
       <c r="O89" t="n">
         <v>590</v>
       </c>
+      <c r="P89" t="n">
+        <v>590</v>
+      </c>
       <c r="R89" t="n">
         <v>0.1698937810403047</v>
       </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -13835,23 +12789,13 @@
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR89" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr"/>
       <c r="AT89" t="n">
         <v>0</v>
       </c>
-      <c r="AU89" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV89" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -13965,14 +12909,12 @@
       <c r="O90" t="n">
         <v>635</v>
       </c>
+      <c r="P90" t="n">
+        <v>635</v>
+      </c>
       <c r="R90" t="n">
         <v>0.1828517812891415</v>
       </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -13985,23 +12927,13 @@
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR90" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="n">
         <v>0</v>
       </c>
-      <c r="AU90" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV90" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -14115,14 +13047,12 @@
       <c r="O91" t="n">
         <v>530</v>
       </c>
+      <c r="P91" t="n">
+        <v>530</v>
+      </c>
       <c r="R91" t="n">
         <v>0.152616447375189</v>
       </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -14135,23 +13065,13 @@
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR91" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="n">
         <v>0</v>
       </c>
-      <c r="AU91" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV91" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -14265,14 +13185,12 @@
       <c r="O92" t="n">
         <v>609</v>
       </c>
+      <c r="P92" t="n">
+        <v>609</v>
+      </c>
       <c r="R92" t="n">
         <v>0.1753649367009247</v>
       </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -14285,23 +13203,13 @@
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR92" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="n">
         <v>0</v>
       </c>
-      <c r="AU92" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV92" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -14415,14 +13323,12 @@
       <c r="O93" t="n">
         <v>707</v>
       </c>
+      <c r="P93" t="n">
+        <v>707</v>
+      </c>
       <c r="R93" t="n">
         <v>0.2035845816872804</v>
       </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -14435,23 +13341,13 @@
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR93" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS93" t="inlineStr"/>
       <c r="AT93" t="n">
         <v>0</v>
       </c>
-      <c r="AU93" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV93" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -14565,14 +13461,12 @@
       <c r="O94" t="n">
         <v>640</v>
       </c>
+      <c r="P94" t="n">
+        <v>640</v>
+      </c>
       <c r="R94" t="n">
         <v>0.1842915590945678</v>
       </c>
-      <c r="S94" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -14585,23 +13479,13 @@
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR94" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="n">
         <v>0</v>
       </c>
-      <c r="AU94" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV94" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -14715,14 +13599,12 @@
       <c r="O95" t="n">
         <v>569</v>
       </c>
+      <c r="P95" t="n">
+        <v>569</v>
+      </c>
       <c r="R95" t="n">
         <v>0.1638467142575142</v>
       </c>
-      <c r="S95" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -14735,23 +13617,13 @@
       </c>
       <c r="AP95" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR95" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="n">
         <v>0</v>
       </c>
-      <c r="AU95" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV95" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -14865,14 +13737,12 @@
       <c r="O96" t="n">
         <v>656</v>
       </c>
+      <c r="P96" t="n">
+        <v>656</v>
+      </c>
       <c r="R96" t="n">
         <v>0.188898848071932</v>
       </c>
-      <c r="S96" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -14885,23 +13755,13 @@
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR96" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="n">
         <v>0</v>
       </c>
-      <c r="AU96" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV96" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -15015,14 +13875,12 @@
       <c r="O97" t="n">
         <v>580</v>
       </c>
+      <c r="P97" t="n">
+        <v>580</v>
+      </c>
       <c r="R97" t="n">
         <v>0.1670142254294521</v>
       </c>
-      <c r="S97" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -15035,23 +13893,13 @@
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR97" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="n">
         <v>0</v>
       </c>
-      <c r="AU97" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV97" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -15165,14 +14013,12 @@
       <c r="O98" t="n">
         <v>647</v>
       </c>
+      <c r="P98" t="n">
+        <v>647</v>
+      </c>
       <c r="R98" t="n">
         <v>0.1863072480221646</v>
       </c>
-      <c r="S98" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -15185,23 +14031,13 @@
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR98" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="n">
         <v>0</v>
       </c>
-      <c r="AU98" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV98" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -15315,14 +14151,12 @@
       <c r="O99" t="n">
         <v>629</v>
       </c>
+      <c r="P99" t="n">
+        <v>629</v>
+      </c>
       <c r="R99" t="n">
         <v>0.1811240479226299</v>
       </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -15335,23 +14169,13 @@
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR99" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="n">
         <v>0</v>
       </c>
-      <c r="AU99" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV99" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -15465,14 +14289,12 @@
       <c r="O100" t="n">
         <v>672</v>
       </c>
+      <c r="P100" t="n">
+        <v>672</v>
+      </c>
       <c r="R100" t="n">
         <v>0.1935061370492962</v>
       </c>
-      <c r="S100" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -15485,23 +14307,13 @@
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR100" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="n">
         <v>0</v>
       </c>
-      <c r="AU100" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV100" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -15615,14 +14427,12 @@
       <c r="O101" t="n">
         <v>447</v>
       </c>
+      <c r="P101" t="n">
+        <v>447</v>
+      </c>
       <c r="R101" t="n">
         <v>0.1287161358051122</v>
       </c>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -15635,23 +14445,13 @@
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR101" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS101" t="inlineStr"/>
       <c r="AT101" t="n">
         <v>0</v>
       </c>
-      <c r="AU101" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV101" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -15765,14 +14565,12 @@
       <c r="O102" t="n">
         <v>497</v>
       </c>
+      <c r="P102" t="n">
+        <v>497</v>
+      </c>
       <c r="R102" t="n">
         <v>0.1431139138593753</v>
       </c>
-      <c r="S102" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -15785,23 +14583,13 @@
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR102" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS102" t="inlineStr"/>
       <c r="AT102" t="n">
         <v>0</v>
       </c>
-      <c r="AU102" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV102" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -15915,14 +14703,12 @@
       <c r="O103" t="n">
         <v>528</v>
       </c>
+      <c r="P103" t="n">
+        <v>528</v>
+      </c>
       <c r="R103" t="n">
         <v>0.1520405362530184</v>
       </c>
-      <c r="S103" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -15935,23 +14721,13 @@
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR103" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS103" t="inlineStr"/>
       <c r="AT103" t="n">
         <v>0</v>
       </c>
-      <c r="AU103" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV103" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -16065,14 +14841,12 @@
       <c r="O104" t="n">
         <v>850</v>
       </c>
+      <c r="P104" t="n">
+        <v>850</v>
+      </c>
       <c r="R104" t="n">
         <v>0.2447622269224729</v>
       </c>
-      <c r="S104" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -16085,23 +14859,13 @@
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR104" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr"/>
       <c r="AT104" t="n">
         <v>0</v>
       </c>
-      <c r="AU104" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV104" t="inlineStr">
         <is>
           <t>nndss_api</t>
@@ -16215,14 +14979,12 @@
       <c r="O105" t="n">
         <v>439</v>
       </c>
+      <c r="P105" t="n">
+        <v>439</v>
+      </c>
       <c r="R105" t="n">
         <v>0.1264124913164301</v>
       </c>
-      <c r="S105" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -16235,22 +14997,12 @@
       </c>
       <c r="AP105" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR105" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS105" t="inlineStr"/>
       <c r="AT105" t="n">
         <v>0</v>
-      </c>
-      <c r="AU105" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV105" t="inlineStr">
         <is>
